--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484638_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484638_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9843</v>
+        <v>7.8666</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4655</v>
+        <v>3.2487</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5188</v>
+        <v>4.6179</v>
       </c>
       <c r="G2" t="n">
         <v>5.0465</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1617</v>
+        <v>-0.2794</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.23</v>
+        <v>-0.4468</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0683</v>
+        <v>0.1674</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.103</v>
+        <v>4.6746</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7576</v>
+        <v>0.3293</v>
       </c>
       <c r="F3" t="n">
         <v>4.3454</v>
@@ -688,10 +688,10 @@
         <v>3.4819</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1976</v>
+        <v>0.7692</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0483</v>
+        <v>0.6199</v>
       </c>
       <c r="U3" t="n">
         <v>0.1493</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8775</v>
+        <v>3.7336</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3119</v>
+        <v>0.2379</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1894</v>
+        <v>3.4957</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0265</v>
@@ -766,13 +766,13 @@
         <v>3.4819</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2547</v>
+        <v>0.1108</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5709</v>
+        <v>-0.0211</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8256</v>
+        <v>0.1319</v>
       </c>
       <c r="V4" t="n">
         <v>1.267</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5189</v>
+        <v>2.7241</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3429</v>
+        <v>-0.6175</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8618</v>
+        <v>3.3416</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6251</v>
@@ -844,13 +844,13 @@
         <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>1.982</v>
+        <v>1.1872</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6395</v>
+        <v>0.365</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3424</v>
+        <v>0.8222</v>
       </c>
       <c r="V5" t="n">
         <v>3.8113</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0906</v>
+        <v>1.484</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6864</v>
+        <v>-1.5903</v>
       </c>
       <c r="F6" t="n">
-        <v>2.777</v>
+        <v>3.0743</v>
       </c>
       <c r="G6" t="n">
         <v>2.3693</v>
@@ -922,13 +922,13 @@
         <v>3.1154</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4149</v>
+        <v>-1.0215</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6802</v>
+        <v>-0.5841</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7347</v>
+        <v>-0.4374</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8796</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AVIÑO GOMEZ-SENENT</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3251</v>
+        <v>0.3701</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3251</v>
+        <v>0.628</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.2579</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3251</v>
+        <v>-1.2699</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3251</v>
+        <v>0.1951</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3251</v>
+        <v>-0.1691</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3251</v>
+        <v>0.4302</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.5994</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.1008</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.2351</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.8656</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.5954</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3469</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2485</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>J. AVIÑO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2104</v>
+        <v>0.3251</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5179</v>
+        <v>0.3251</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3075</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2699</v>
+        <v>0.3251</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1951</v>
+        <v>0.3251</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.465</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1691</v>
+        <v>0.3251</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4302</v>
+        <v>0.3251</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5994</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1008</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2351</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8656</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4357</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2368</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1989</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0984</v>
+        <v>-0.3126</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2181</v>
+        <v>-0.0704</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3165</v>
+        <v>-0.2422</v>
       </c>
       <c r="G11" t="n">
         <v>0.5119</v>
@@ -1312,13 +1312,13 @@
         <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4271</v>
+        <v>-0.6412</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4208</v>
+        <v>0.1324</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8479</v>
+        <v>-0.7736</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. AVINO GOMEZ-SENENT</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5116</v>
+        <v>-1.0354</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7338</v>
+        <v>-1.0257</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2222</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2714</v>
+        <v>-3.2896</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6881</v>
+        <v>-1.5587</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5833</v>
+        <v>-1.7309</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6328</v>
+        <v>-2.4774</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.152</v>
+        <v>-1.1954</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.4808</v>
+        <v>-1.2821</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3614</v>
+        <v>-0.8122</v>
       </c>
       <c r="N12" t="n">
-        <v>0.464</v>
+        <v>-0.3633</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8974</v>
+        <v>-0.4489</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1565</v>
+        <v>0.2151</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1847</v>
+        <v>0.1456</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0283</v>
+        <v>0.0696</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>J. AVINO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8026</v>
+        <v>-1.6762</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5205</v>
+        <v>-5.0223</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2821</v>
+        <v>3.3461</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.2896</v>
+        <v>-2.2714</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5587</v>
+        <v>-0.6881</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7309</v>
+        <v>-1.5833</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.4774</v>
+        <v>-3.6328</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1954</v>
+        <v>-1.152</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2821</v>
+        <v>-2.4808</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8122</v>
+        <v>1.3614</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3633</v>
+        <v>0.464</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4489</v>
+        <v>0.8974</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5521</v>
+        <v>-0.3211</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3492</v>
+        <v>-0.4732</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2029</v>
+        <v>0.1521</v>
       </c>
       <c r="V13" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.385</v>
+        <v>-2.5767</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.5808</v>
+        <v>-2.045</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8042</v>
+        <v>-0.5317</v>
       </c>
       <c r="G14" t="n">
         <v>-1.1262</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8085</v>
+        <v>-0.0002</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4774</v>
+        <v>0.0585</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3312</v>
+        <v>-0.0586</v>
       </c>
       <c r="V14" t="n">
         <v>-1.267</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.0458</v>
+        <v>-3.4852</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.7323</v>
+        <v>-4.1965</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6865</v>
+        <v>0.7113</v>
       </c>
       <c r="G15" t="n">
         <v>-2.6883</v>
@@ -1624,13 +1624,13 @@
         <v>1.0995</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.0639</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4223</v>
+        <v>0.1135</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2022</v>
+        <v>-0.1774</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.91659999999999</v>
+        <v>12.7422</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.9742</v>
+        <v>-9.1485</v>
       </c>
       <c r="F16" t="n">
-        <v>21.8908</v>
+        <v>21.8909</v>
       </c>
       <c r="G16" t="n">
         <v>0.7180000000000009</v>
@@ -1702,13 +1702,13 @@
         <v>20.1582</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2753000000000005</v>
+        <v>0.5504000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5693000000000001</v>
+        <v>0.2566000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2939000000000001</v>
+        <v>0.2939999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>4.143700000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>M. CALANCHE GONZÁLEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1764</v>
+        <v>0.9502</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6319</v>
+        <v>0.9502</v>
       </c>
       <c r="F17" t="n">
-        <v>5.8083</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5159</v>
+        <v>0.9502</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2335</v>
+        <v>0.3251</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7176</v>
+        <v>0.6251</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.512</v>
+        <v>0.9502</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5953</v>
+        <v>0.3251</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0833</v>
+        <v>0.6251</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9961</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6382</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.6342</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8484</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2683</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.773</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4952</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2566</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZÁLEZ</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9502</v>
+        <v>0.4575</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9502</v>
+        <v>-4.1704</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4.6278</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9502</v>
+        <v>-0.5159</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3251</v>
+        <v>-2.2335</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6251</v>
+        <v>1.7176</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9502</v>
+        <v>-1.512</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3251</v>
+        <v>-1.5953</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6251</v>
+        <v>0.0833</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.9961</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.6382</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.8484</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.5494</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.2346</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3148</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2566</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4814</v>
+        <v>0.2469</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2055</v>
+        <v>-0.494</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6869</v>
+        <v>0.7408</v>
       </c>
       <c r="G19" t="n">
         <v>0.2746</v>
@@ -1936,13 +1936,13 @@
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5734</v>
+        <v>0.3388</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6041</v>
+        <v>0.3156</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0307</v>
+        <v>0.0232</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5668</v>
+        <v>0.0189</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7026</v>
+        <v>-0.4141</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1358</v>
+        <v>0.4331</v>
       </c>
       <c r="G20" t="n">
         <v>0.7855</v>
@@ -2014,13 +2014,13 @@
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3523</v>
+        <v>0.2334</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2941</v>
+        <v>-0.0056</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0582</v>
+        <v>0.2391</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6335</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0304</v>
+        <v>-0.0132</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7839</v>
+        <v>-0.6318</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7535</v>
+        <v>0.6186</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.399</v>
+        <v>0.6826</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0849</v>
+        <v>0.8942</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3142</v>
+        <v>-0.2116</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7191</v>
+        <v>-0.3</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.155</v>
+        <v>1.5139</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5641</v>
+        <v>-1.814</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3201</v>
+        <v>0.9827</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0701</v>
+        <v>-0.6198</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2499</v>
+        <v>1.6024</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3241</v>
+        <v>-0.2064</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0347</v>
+        <v>-0.1485</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2893</v>
+        <v>-0.0579</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3114</v>
+        <v>-0.6782</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4011</v>
+        <v>-3.3859</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0897</v>
+        <v>2.7077</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6826</v>
+        <v>0.151</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8942</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2116</v>
+        <v>1.0991</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3</v>
+        <v>-1.352</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5139</v>
+        <v>-0.7527</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.814</v>
+        <v>-0.5994</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9827</v>
+        <v>1.503</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6198</v>
+        <v>-0.1955</v>
       </c>
       <c r="O22" t="n">
-        <v>1.6024</v>
+        <v>1.6985</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0995</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5046</v>
+        <v>-0.3528</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.3688</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5868</v>
+        <v>0.016</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5889</v>
+        <v>0.6231</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5889</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1046</v>
+        <v>-1.0202</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1552</v>
+        <v>-3.9762</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0506</v>
+        <v>2.956</v>
       </c>
       <c r="G23" t="n">
-        <v>0.151</v>
+        <v>-1.399</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.0849</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0991</v>
+        <v>-1.3142</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.352</v>
+        <v>-2.7191</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7527</v>
+        <v>-0.155</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5994</v>
+        <v>-2.5641</v>
       </c>
       <c r="M23" t="n">
-        <v>1.503</v>
+        <v>1.3201</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1955</v>
+        <v>0.0701</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6985</v>
+        <v>1.2499</v>
       </c>
       <c r="P23" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.0995</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-2.9321</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7791</v>
+        <v>0.3343</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.138</v>
+        <v>-0.1576</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6411</v>
+        <v>0.4919</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
       <c r="W23" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3927</v>
+        <v>-1.7442</v>
       </c>
       <c r="E24" t="n">
         <v>-2.6229</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2302</v>
+        <v>0.8787</v>
       </c>
       <c r="G24" t="n">
         <v>1.0214</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>0.052</v>
+        <v>0.7004</v>
       </c>
       <c r="T24" t="n">
         <v>0.3454</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2935</v>
+        <v>0.355</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9995</v>
+        <v>-2.9448</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3492</v>
+        <v>-1.58</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6503</v>
+        <v>-1.3647</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5964</v>
@@ -2404,13 +2404,13 @@
         <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7983</v>
+        <v>0.2564</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8084</v>
+        <v>-0.0392</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0101</v>
+        <v>0.2956</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3219</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.1194</v>
+        <v>-5.2665</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9887</v>
+        <v>-5.5656</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1307</v>
+        <v>0.2992</v>
       </c>
       <c r="G26" t="n">
         <v>-1.0719</v>
@@ -2482,13 +2482,13 @@
         <v>2.1991</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5081</v>
+        <v>-0.6552</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1071</v>
+        <v>-0.4698</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6152</v>
+        <v>-0.1854</v>
       </c>
       <c r="V26" t="n">
         <v>-1.89</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.9168</v>
+        <v>-9.993600000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-21.8908</v>
+        <v>-21.8907</v>
       </c>
       <c r="F27" t="n">
-        <v>9.974000000000002</v>
+        <v>11.8972</v>
       </c>
       <c r="G27" t="n">
         <v>-0.7179</v>
@@ -2560,13 +2560,13 @@
         <v>12.8282</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2754000000000003</v>
+        <v>2.1983</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2940000000000003</v>
+        <v>-0.2939000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5690999999999999</v>
+        <v>2.4923</v>
       </c>
       <c r="V27" t="n">
         <v>-4.1435</v>
